--- a/output/2026-10-03_20_Malesia_Pulau_Pinang_Cleaning.xlsx
+++ b/output/2026-10-03_20_Malesia_Pulau_Pinang_Cleaning.xlsx
@@ -478,7 +478,6 @@
           <t>Qbox Resources Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Bandar Cassia, Seberang Perai Selatan, Pulau Pinang</t>
@@ -494,7 +493,6 @@
           <t>604-584 4888 / 6012-548 7298</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Esistenza confermata (indirizzo e telefono coincidenti con fonti pubbliche; director: Chamby Toh). Distributore one-stop di prodotti industriali: cleanroom, ESD, PPE, con consulenza/attrezzature per ambienti puliti controllati. Focus principale su cleanroom/ESD piu' che su pulizia industriale generica: verificare pertinenza col target.</t>
@@ -527,8 +525,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Confermata esistenza del Karcher Centre di Bayan Baru come sede ufficiale a Penang (oltre a Shah Alam e Johor Bahru). La ragione sociale e' la filiale malese del produttore Karcher, con sede legale a Shah Alam, Selangor. Indirizzo esatto e contatti diretti della sede di Bayan Baru non reperiti online, lasciati vuoti.</t>
@@ -536,7 +532,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -546,7 +542,6 @@
           <t>Super Starnix Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Pulau Pinang (indirizzo esatto non reperito)</t>
@@ -557,8 +552,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Confermata tramite Invest Penang SME Directory come fornitore di ESD &amp; Cleanroom Supplies e Safety Products, general trading industriale. Focus principale su cleanroom/ESD piu' che pulizia industriale generica: verificare pertinenza col target.</t>
@@ -576,7 +569,6 @@
           <t>OSS Ventures Worldwide Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Pulau Pinang (indirizzo esatto non reperito)</t>
@@ -587,8 +579,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Confermata tramite Invest Penang SME Directory come distributore/produttore di materiali di consumo per cleanroom e DPI industriali. Focus principale su cleanroom/ESD: verificare pertinenza col target.</t>
@@ -596,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -621,8 +611,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Confermato profilo fornitore reale sulla piattaforma B2B Lapasar Mall, indirizzo coincidente. Distributore di prodotti Cleaning, Hygiene &amp; Janitorial (es. detergenti/sgrassanti marchio Ajax Fabuloso). Buon fit col settore target. Telefono ed email non reperiti pubblicamente.</t>
@@ -630,7 +618,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -667,7 +655,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Azienda confermata via sito ufficiale (telefono coincidente). Produttore/distributore DPI con divisione dedicata 'Cleanware - Hygiene &amp; Sanitisation Solutions' (detergenti, disinfettanti, sanificanti, abbigliamento monouso). Buon fit col settore target.</t>
+          <t>Azienda confermata via sito ufficiale (telefono coincidente). Produttore/distributore DPI con divisione dedicata 'Cleanware - Hygiene &amp; Sanitisation Solutions' (detergenti, disinfettanti, sanificanti, abbigliamento monouso). Buon fit col settore target. [DUPLICATO — vedi anche: 2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
